--- a/outputs/analysis/Mixed_Metabolic_Cohort/Mixed_Metabolic_Cohort_MANDOROS_Master_Report.xlsx
+++ b/outputs/analysis/Mixed_Metabolic_Cohort/Mixed_Metabolic_Cohort_MANDOROS_Master_Report.xlsx
@@ -389,7 +389,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>334</col>
+      <col>274</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
@@ -1904,7 +1904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:LU7"/>
+  <dimension ref="A1:JM7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1999,7 +1999,7 @@
     <col width="12" customWidth="1" min="90" max="90"/>
     <col width="12" customWidth="1" min="91" max="91"/>
     <col width="12" customWidth="1" min="92" max="92"/>
-    <col width="29" customWidth="1" min="93" max="93"/>
+    <col width="12" customWidth="1" min="93" max="93"/>
     <col width="12" customWidth="1" min="94" max="94"/>
     <col width="12" customWidth="1" min="95" max="95"/>
     <col width="13" customWidth="1" min="96" max="96"/>
@@ -2010,7 +2010,7 @@
     <col width="12" customWidth="1" min="101" max="101"/>
     <col width="12" customWidth="1" min="102" max="102"/>
     <col width="12" customWidth="1" min="103" max="103"/>
-    <col width="36" customWidth="1" min="104" max="104"/>
+    <col width="12" customWidth="1" min="104" max="104"/>
     <col width="12" customWidth="1" min="105" max="105"/>
     <col width="12" customWidth="1" min="106" max="106"/>
     <col width="13" customWidth="1" min="107" max="107"/>
@@ -2021,7 +2021,7 @@
     <col width="12" customWidth="1" min="112" max="112"/>
     <col width="12" customWidth="1" min="113" max="113"/>
     <col width="12" customWidth="1" min="114" max="114"/>
-    <col width="28" customWidth="1" min="115" max="115"/>
+    <col width="12" customWidth="1" min="115" max="115"/>
     <col width="12" customWidth="1" min="116" max="116"/>
     <col width="12" customWidth="1" min="117" max="117"/>
     <col width="13" customWidth="1" min="118" max="118"/>
@@ -2032,7 +2032,7 @@
     <col width="12" customWidth="1" min="123" max="123"/>
     <col width="12" customWidth="1" min="124" max="124"/>
     <col width="12" customWidth="1" min="125" max="125"/>
-    <col width="25" customWidth="1" min="126" max="126"/>
+    <col width="20" customWidth="1" min="126" max="126"/>
     <col width="12" customWidth="1" min="127" max="127"/>
     <col width="12" customWidth="1" min="128" max="128"/>
     <col width="13" customWidth="1" min="129" max="129"/>
@@ -2043,7 +2043,7 @@
     <col width="12" customWidth="1" min="134" max="134"/>
     <col width="12" customWidth="1" min="135" max="135"/>
     <col width="12" customWidth="1" min="136" max="136"/>
-    <col width="35" customWidth="1" min="137" max="137"/>
+    <col width="12" customWidth="1" min="137" max="137"/>
     <col width="12" customWidth="1" min="138" max="138"/>
     <col width="12" customWidth="1" min="139" max="139"/>
     <col width="13" customWidth="1" min="140" max="140"/>
@@ -2065,7 +2065,7 @@
     <col width="12" customWidth="1" min="156" max="156"/>
     <col width="12" customWidth="1" min="157" max="157"/>
     <col width="12" customWidth="1" min="158" max="158"/>
-    <col width="12" customWidth="1" min="159" max="159"/>
+    <col width="16" customWidth="1" min="159" max="159"/>
     <col width="12" customWidth="1" min="160" max="160"/>
     <col width="12" customWidth="1" min="161" max="161"/>
     <col width="13" customWidth="1" min="162" max="162"/>
@@ -2076,7 +2076,7 @@
     <col width="12" customWidth="1" min="167" max="167"/>
     <col width="12" customWidth="1" min="168" max="168"/>
     <col width="12" customWidth="1" min="169" max="169"/>
-    <col width="12" customWidth="1" min="170" max="170"/>
+    <col width="18" customWidth="1" min="170" max="170"/>
     <col width="12" customWidth="1" min="171" max="171"/>
     <col width="12" customWidth="1" min="172" max="172"/>
     <col width="13" customWidth="1" min="173" max="173"/>
@@ -2087,7 +2087,7 @@
     <col width="12" customWidth="1" min="178" max="178"/>
     <col width="12" customWidth="1" min="179" max="179"/>
     <col width="12" customWidth="1" min="180" max="180"/>
-    <col width="20" customWidth="1" min="181" max="181"/>
+    <col width="12" customWidth="1" min="181" max="181"/>
     <col width="12" customWidth="1" min="182" max="182"/>
     <col width="12" customWidth="1" min="183" max="183"/>
     <col width="13" customWidth="1" min="184" max="184"/>
@@ -2098,7 +2098,7 @@
     <col width="12" customWidth="1" min="189" max="189"/>
     <col width="12" customWidth="1" min="190" max="190"/>
     <col width="12" customWidth="1" min="191" max="191"/>
-    <col width="12" customWidth="1" min="192" max="192"/>
+    <col width="25" customWidth="1" min="192" max="192"/>
     <col width="12" customWidth="1" min="193" max="193"/>
     <col width="12" customWidth="1" min="194" max="194"/>
     <col width="13" customWidth="1" min="195" max="195"/>
@@ -2120,7 +2120,7 @@
     <col width="12" customWidth="1" min="211" max="211"/>
     <col width="12" customWidth="1" min="212" max="212"/>
     <col width="12" customWidth="1" min="213" max="213"/>
-    <col width="16" customWidth="1" min="214" max="214"/>
+    <col width="13" customWidth="1" min="214" max="214"/>
     <col width="12" customWidth="1" min="215" max="215"/>
     <col width="12" customWidth="1" min="216" max="216"/>
     <col width="13" customWidth="1" min="217" max="217"/>
@@ -2131,7 +2131,7 @@
     <col width="12" customWidth="1" min="222" max="222"/>
     <col width="12" customWidth="1" min="223" max="223"/>
     <col width="12" customWidth="1" min="224" max="224"/>
-    <col width="18" customWidth="1" min="225" max="225"/>
+    <col width="12" customWidth="1" min="225" max="225"/>
     <col width="12" customWidth="1" min="226" max="226"/>
     <col width="12" customWidth="1" min="227" max="227"/>
     <col width="13" customWidth="1" min="228" max="228"/>
@@ -2153,7 +2153,7 @@
     <col width="12" customWidth="1" min="244" max="244"/>
     <col width="12" customWidth="1" min="245" max="245"/>
     <col width="12" customWidth="1" min="246" max="246"/>
-    <col width="25" customWidth="1" min="247" max="247"/>
+    <col width="12" customWidth="1" min="247" max="247"/>
     <col width="12" customWidth="1" min="248" max="248"/>
     <col width="12" customWidth="1" min="249" max="249"/>
     <col width="13" customWidth="1" min="250" max="250"/>
@@ -2175,71 +2175,11 @@
     <col width="12" customWidth="1" min="266" max="266"/>
     <col width="12" customWidth="1" min="267" max="267"/>
     <col width="12" customWidth="1" min="268" max="268"/>
-    <col width="13" customWidth="1" min="269" max="269"/>
-    <col width="12" customWidth="1" min="270" max="270"/>
-    <col width="12" customWidth="1" min="271" max="271"/>
-    <col width="13" customWidth="1" min="272" max="272"/>
-    <col width="17" customWidth="1" min="273" max="273"/>
-    <col width="23" customWidth="1" min="274" max="274"/>
-    <col width="18" customWidth="1" min="275" max="275"/>
-    <col width="12" customWidth="1" min="276" max="276"/>
-    <col width="12" customWidth="1" min="277" max="277"/>
-    <col width="12" customWidth="1" min="278" max="278"/>
-    <col width="12" customWidth="1" min="279" max="279"/>
-    <col width="12" customWidth="1" min="280" max="280"/>
-    <col width="12" customWidth="1" min="281" max="281"/>
-    <col width="12" customWidth="1" min="282" max="282"/>
-    <col width="13" customWidth="1" min="283" max="283"/>
-    <col width="17" customWidth="1" min="284" max="284"/>
-    <col width="23" customWidth="1" min="285" max="285"/>
-    <col width="18" customWidth="1" min="286" max="286"/>
-    <col width="12" customWidth="1" min="287" max="287"/>
-    <col width="12" customWidth="1" min="288" max="288"/>
-    <col width="12" customWidth="1" min="289" max="289"/>
-    <col width="12" customWidth="1" min="290" max="290"/>
-    <col width="12" customWidth="1" min="291" max="291"/>
-    <col width="12" customWidth="1" min="292" max="292"/>
-    <col width="12" customWidth="1" min="293" max="293"/>
-    <col width="13" customWidth="1" min="294" max="294"/>
-    <col width="17" customWidth="1" min="295" max="295"/>
-    <col width="23" customWidth="1" min="296" max="296"/>
-    <col width="18" customWidth="1" min="297" max="297"/>
-    <col width="12" customWidth="1" min="298" max="298"/>
-    <col width="12" customWidth="1" min="299" max="299"/>
-    <col width="12" customWidth="1" min="300" max="300"/>
-    <col width="12" customWidth="1" min="301" max="301"/>
-    <col width="12" customWidth="1" min="302" max="302"/>
-    <col width="12" customWidth="1" min="303" max="303"/>
-    <col width="12" customWidth="1" min="304" max="304"/>
-    <col width="13" customWidth="1" min="305" max="305"/>
-    <col width="17" customWidth="1" min="306" max="306"/>
-    <col width="23" customWidth="1" min="307" max="307"/>
-    <col width="18" customWidth="1" min="308" max="308"/>
-    <col width="12" customWidth="1" min="309" max="309"/>
-    <col width="12" customWidth="1" min="310" max="310"/>
-    <col width="12" customWidth="1" min="311" max="311"/>
-    <col width="12" customWidth="1" min="312" max="312"/>
-    <col width="12" customWidth="1" min="313" max="313"/>
-    <col width="12" customWidth="1" min="314" max="314"/>
-    <col width="12" customWidth="1" min="315" max="315"/>
-    <col width="13" customWidth="1" min="316" max="316"/>
-    <col width="17" customWidth="1" min="317" max="317"/>
-    <col width="23" customWidth="1" min="318" max="318"/>
-    <col width="18" customWidth="1" min="319" max="319"/>
-    <col width="12" customWidth="1" min="320" max="320"/>
-    <col width="12" customWidth="1" min="321" max="321"/>
-    <col width="12" customWidth="1" min="322" max="322"/>
-    <col width="12" customWidth="1" min="323" max="323"/>
-    <col width="37" customWidth="1" min="324" max="324"/>
-    <col width="18" customWidth="1" min="325" max="325"/>
-    <col width="17" customWidth="1" min="326" max="326"/>
-    <col width="28" customWidth="1" min="327" max="327"/>
-    <col width="12" customWidth="1" min="328" max="328"/>
-    <col width="30" customWidth="1" min="329" max="329"/>
-    <col width="18" customWidth="1" min="330" max="330"/>
-    <col width="17" customWidth="1" min="331" max="331"/>
-    <col width="28" customWidth="1" min="332" max="332"/>
-    <col width="12" customWidth="1" min="333" max="333"/>
+    <col width="30" customWidth="1" min="269" max="269"/>
+    <col width="18" customWidth="1" min="270" max="270"/>
+    <col width="17" customWidth="1" min="271" max="271"/>
+    <col width="28" customWidth="1" min="272" max="272"/>
+    <col width="12" customWidth="1" min="273" max="273"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2531,75 +2471,15 @@
       <c r="JF1" s="1" t="n"/>
       <c r="JG1" s="1" t="n"/>
       <c r="JH1" s="1" t="n"/>
-      <c r="JI1" s="1" t="n"/>
+      <c r="JI1" s="1" t="inlineStr">
+        <is>
+          <t>5. SAFETY OUTCOMES</t>
+        </is>
+      </c>
       <c r="JJ1" s="1" t="n"/>
       <c r="JK1" s="1" t="n"/>
       <c r="JL1" s="1" t="n"/>
       <c r="JM1" s="1" t="n"/>
-      <c r="JN1" s="1" t="n"/>
-      <c r="JO1" s="1" t="n"/>
-      <c r="JP1" s="1" t="n"/>
-      <c r="JQ1" s="1" t="n"/>
-      <c r="JR1" s="1" t="n"/>
-      <c r="JS1" s="1" t="n"/>
-      <c r="JT1" s="1" t="n"/>
-      <c r="JU1" s="1" t="n"/>
-      <c r="JV1" s="1" t="n"/>
-      <c r="JW1" s="1" t="n"/>
-      <c r="JX1" s="1" t="n"/>
-      <c r="JY1" s="1" t="n"/>
-      <c r="JZ1" s="1" t="n"/>
-      <c r="KA1" s="1" t="n"/>
-      <c r="KB1" s="1" t="n"/>
-      <c r="KC1" s="1" t="n"/>
-      <c r="KD1" s="1" t="n"/>
-      <c r="KE1" s="1" t="n"/>
-      <c r="KF1" s="1" t="n"/>
-      <c r="KG1" s="1" t="n"/>
-      <c r="KH1" s="1" t="n"/>
-      <c r="KI1" s="1" t="n"/>
-      <c r="KJ1" s="1" t="n"/>
-      <c r="KK1" s="1" t="n"/>
-      <c r="KL1" s="1" t="n"/>
-      <c r="KM1" s="1" t="n"/>
-      <c r="KN1" s="1" t="n"/>
-      <c r="KO1" s="1" t="n"/>
-      <c r="KP1" s="1" t="n"/>
-      <c r="KQ1" s="1" t="n"/>
-      <c r="KR1" s="1" t="n"/>
-      <c r="KS1" s="1" t="n"/>
-      <c r="KT1" s="1" t="n"/>
-      <c r="KU1" s="1" t="n"/>
-      <c r="KV1" s="1" t="n"/>
-      <c r="KW1" s="1" t="n"/>
-      <c r="KX1" s="1" t="n"/>
-      <c r="KY1" s="1" t="n"/>
-      <c r="KZ1" s="1" t="n"/>
-      <c r="LA1" s="1" t="n"/>
-      <c r="LB1" s="1" t="n"/>
-      <c r="LC1" s="1" t="n"/>
-      <c r="LD1" s="1" t="n"/>
-      <c r="LE1" s="1" t="n"/>
-      <c r="LF1" s="1" t="n"/>
-      <c r="LG1" s="1" t="n"/>
-      <c r="LH1" s="1" t="n"/>
-      <c r="LI1" s="1" t="n"/>
-      <c r="LJ1" s="1" t="n"/>
-      <c r="LK1" s="1" t="n"/>
-      <c r="LL1" s="1" t="inlineStr">
-        <is>
-          <t>5. SAFETY OUTCOMES</t>
-        </is>
-      </c>
-      <c r="LM1" s="1" t="n"/>
-      <c r="LN1" s="1" t="n"/>
-      <c r="LO1" s="1" t="n"/>
-      <c r="LP1" s="1" t="n"/>
-      <c r="LQ1" s="1" t="n"/>
-      <c r="LR1" s="1" t="n"/>
-      <c r="LS1" s="1" t="n"/>
-      <c r="LT1" s="1" t="n"/>
-      <c r="LU1" s="1" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -2808,7 +2688,7 @@
       <c r="CN2" s="2" t="n"/>
       <c r="CO2" s="2" t="inlineStr">
         <is>
-          <t>high adherence [Caucasian]</t>
+          <t>age</t>
         </is>
       </c>
       <c r="CP2" s="2" t="n"/>
@@ -2823,7 +2703,7 @@
       <c r="CY2" s="2" t="n"/>
       <c r="CZ2" s="2" t="inlineStr">
         <is>
-          <t>high adherence [African American]</t>
+          <t>bmi</t>
         </is>
       </c>
       <c r="DA2" s="2" t="n"/>
@@ -2838,7 +2718,7 @@
       <c r="DJ2" s="2" t="n"/>
       <c r="DK2" s="2" t="inlineStr">
         <is>
-          <t>high adherence [Hispanic]</t>
+          <t>body fat</t>
         </is>
       </c>
       <c r="DL2" s="2" t="n"/>
@@ -2853,7 +2733,7 @@
       <c r="DU2" s="2" t="n"/>
       <c r="DV2" s="2" t="inlineStr">
         <is>
-          <t>high adherence [Asian]</t>
+          <t>total_cholesterol</t>
         </is>
       </c>
       <c r="DW2" s="2" t="n"/>
@@ -2868,7 +2748,7 @@
       <c r="EF2" s="2" t="n"/>
       <c r="EG2" s="2" t="inlineStr">
         <is>
-          <t>high adherence [Native American]</t>
+          <t>hdl-c</t>
         </is>
       </c>
       <c r="EH2" s="2" t="n"/>
@@ -2883,7 +2763,7 @@
       <c r="EQ2" s="2" t="n"/>
       <c r="ER2" s="2" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>ldl-c</t>
         </is>
       </c>
       <c r="ES2" s="2" t="n"/>
@@ -2898,7 +2778,7 @@
       <c r="FB2" s="2" t="n"/>
       <c r="FC2" s="2" t="inlineStr">
         <is>
-          <t>bmi</t>
+          <t>triglycerides</t>
         </is>
       </c>
       <c r="FD2" s="2" t="n"/>
@@ -2913,7 +2793,7 @@
       <c r="FM2" s="2" t="n"/>
       <c r="FN2" s="2" t="inlineStr">
         <is>
-          <t>body fat</t>
+          <t>fasting_glucose</t>
         </is>
       </c>
       <c r="FO2" s="2" t="n"/>
@@ -2928,7 +2808,7 @@
       <c r="FX2" s="2" t="n"/>
       <c r="FY2" s="2" t="inlineStr">
         <is>
-          <t>total_cholesterol</t>
+          <t>hba1c</t>
         </is>
       </c>
       <c r="FZ2" s="2" t="n"/>
@@ -2943,7 +2823,7 @@
       <c r="GI2" s="2" t="n"/>
       <c r="GJ2" s="2" t="inlineStr">
         <is>
-          <t>hdl-c</t>
+          <t>fasting insulin (fins)</t>
         </is>
       </c>
       <c r="GK2" s="2" t="n"/>
@@ -2958,7 +2838,7 @@
       <c r="GT2" s="2" t="n"/>
       <c r="GU2" s="2" t="inlineStr">
         <is>
-          <t>ldl-c</t>
+          <t>egfr</t>
         </is>
       </c>
       <c r="GV2" s="2" t="n"/>
@@ -2973,7 +2853,7 @@
       <c r="HE2" s="2" t="n"/>
       <c r="HF2" s="2" t="inlineStr">
         <is>
-          <t>triglycerides</t>
+          <t>creatinine</t>
         </is>
       </c>
       <c r="HG2" s="2" t="n"/>
@@ -2988,7 +2868,7 @@
       <c r="HP2" s="2" t="n"/>
       <c r="HQ2" s="2" t="inlineStr">
         <is>
-          <t>fasting_glucose</t>
+          <t>urea</t>
         </is>
       </c>
       <c r="HR2" s="2" t="n"/>
@@ -3003,7 +2883,7 @@
       <c r="IA2" s="2" t="n"/>
       <c r="IB2" s="2" t="inlineStr">
         <is>
-          <t>hba1c</t>
+          <t>alt</t>
         </is>
       </c>
       <c r="IC2" s="2" t="n"/>
@@ -3018,7 +2898,7 @@
       <c r="IL2" s="2" t="n"/>
       <c r="IM2" s="2" t="inlineStr">
         <is>
-          <t>fasting insulin (fins)</t>
+          <t>ast</t>
         </is>
       </c>
       <c r="IN2" s="2" t="n"/>
@@ -3031,11 +2911,7 @@
       <c r="IU2" s="2" t="n"/>
       <c r="IV2" s="2" t="n"/>
       <c r="IW2" s="2" t="n"/>
-      <c r="IX2" s="2" t="inlineStr">
-        <is>
-          <t>egfr</t>
-        </is>
-      </c>
+      <c r="IX2" s="2" t="inlineStr"/>
       <c r="IY2" s="2" t="n"/>
       <c r="IZ2" s="2" t="n"/>
       <c r="JA2" s="2" t="n"/>
@@ -3048,93 +2924,13 @@
       <c r="JH2" s="2" t="n"/>
       <c r="JI2" s="2" t="inlineStr">
         <is>
-          <t>creatinine</t>
+          <t>gout flares</t>
         </is>
       </c>
       <c r="JJ2" s="2" t="n"/>
       <c r="JK2" s="2" t="n"/>
       <c r="JL2" s="2" t="n"/>
       <c r="JM2" s="2" t="n"/>
-      <c r="JN2" s="2" t="n"/>
-      <c r="JO2" s="2" t="n"/>
-      <c r="JP2" s="2" t="n"/>
-      <c r="JQ2" s="2" t="n"/>
-      <c r="JR2" s="2" t="n"/>
-      <c r="JS2" s="2" t="n"/>
-      <c r="JT2" s="2" t="inlineStr">
-        <is>
-          <t>urea</t>
-        </is>
-      </c>
-      <c r="JU2" s="2" t="n"/>
-      <c r="JV2" s="2" t="n"/>
-      <c r="JW2" s="2" t="n"/>
-      <c r="JX2" s="2" t="n"/>
-      <c r="JY2" s="2" t="n"/>
-      <c r="JZ2" s="2" t="n"/>
-      <c r="KA2" s="2" t="n"/>
-      <c r="KB2" s="2" t="n"/>
-      <c r="KC2" s="2" t="n"/>
-      <c r="KD2" s="2" t="n"/>
-      <c r="KE2" s="2" t="inlineStr">
-        <is>
-          <t>alt</t>
-        </is>
-      </c>
-      <c r="KF2" s="2" t="n"/>
-      <c r="KG2" s="2" t="n"/>
-      <c r="KH2" s="2" t="n"/>
-      <c r="KI2" s="2" t="n"/>
-      <c r="KJ2" s="2" t="n"/>
-      <c r="KK2" s="2" t="n"/>
-      <c r="KL2" s="2" t="n"/>
-      <c r="KM2" s="2" t="n"/>
-      <c r="KN2" s="2" t="n"/>
-      <c r="KO2" s="2" t="n"/>
-      <c r="KP2" s="2" t="inlineStr">
-        <is>
-          <t>ast</t>
-        </is>
-      </c>
-      <c r="KQ2" s="2" t="n"/>
-      <c r="KR2" s="2" t="n"/>
-      <c r="KS2" s="2" t="n"/>
-      <c r="KT2" s="2" t="n"/>
-      <c r="KU2" s="2" t="n"/>
-      <c r="KV2" s="2" t="n"/>
-      <c r="KW2" s="2" t="n"/>
-      <c r="KX2" s="2" t="n"/>
-      <c r="KY2" s="2" t="n"/>
-      <c r="KZ2" s="2" t="n"/>
-      <c r="LA2" s="2" t="inlineStr"/>
-      <c r="LB2" s="2" t="n"/>
-      <c r="LC2" s="2" t="n"/>
-      <c r="LD2" s="2" t="n"/>
-      <c r="LE2" s="2" t="n"/>
-      <c r="LF2" s="2" t="n"/>
-      <c r="LG2" s="2" t="n"/>
-      <c r="LH2" s="2" t="n"/>
-      <c r="LI2" s="2" t="n"/>
-      <c r="LJ2" s="2" t="n"/>
-      <c r="LK2" s="2" t="n"/>
-      <c r="LL2" s="2" t="inlineStr">
-        <is>
-          <t>gout flares [GEOMETRIC_MEAN_RATIO]</t>
-        </is>
-      </c>
-      <c r="LM2" s="2" t="n"/>
-      <c r="LN2" s="2" t="n"/>
-      <c r="LO2" s="2" t="n"/>
-      <c r="LP2" s="2" t="n"/>
-      <c r="LQ2" s="2" t="inlineStr">
-        <is>
-          <t>gout flares</t>
-        </is>
-      </c>
-      <c r="LR2" s="2" t="n"/>
-      <c r="LS2" s="2" t="n"/>
-      <c r="LT2" s="2" t="n"/>
-      <c r="LU2" s="2" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr"/>
@@ -4447,325 +4243,25 @@
       </c>
       <c r="JI3" s="4" t="inlineStr">
         <is>
-          <t>Mean</t>
+          <t>Participants with Event (n)</t>
         </is>
       </c>
       <c r="JJ3" s="4" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>Denominator (N)</t>
         </is>
       </c>
       <c r="JK3" s="4" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>Percentage (%)</t>
         </is>
       </c>
       <c r="JL3" s="4" t="inlineStr">
         <is>
-          <t>Events (n)</t>
+          <t>Observation Period</t>
         </is>
       </c>
       <c r="JM3" s="4" t="inlineStr">
-        <is>
-          <t>Percentage (%)</t>
-        </is>
-      </c>
-      <c r="JN3" s="4" t="inlineStr">
-        <is>
-          <t>Change from Baseline</t>
-        </is>
-      </c>
-      <c r="JO3" s="4" t="inlineStr">
-        <is>
-          <t>Effect Estimate</t>
-        </is>
-      </c>
-      <c r="JP3" s="4" t="inlineStr">
-        <is>
-          <t>CI Lower</t>
-        </is>
-      </c>
-      <c r="JQ3" s="4" t="inlineStr">
-        <is>
-          <t>CI Upper</t>
-        </is>
-      </c>
-      <c r="JR3" s="4" t="inlineStr">
-        <is>
-          <t>P-value</t>
-        </is>
-      </c>
-      <c r="JS3" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="JT3" s="4" t="inlineStr">
-        <is>
-          <t>Mean</t>
-        </is>
-      </c>
-      <c r="JU3" s="4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="JV3" s="4" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="JW3" s="4" t="inlineStr">
-        <is>
-          <t>Events (n)</t>
-        </is>
-      </c>
-      <c r="JX3" s="4" t="inlineStr">
-        <is>
-          <t>Percentage (%)</t>
-        </is>
-      </c>
-      <c r="JY3" s="4" t="inlineStr">
-        <is>
-          <t>Change from Baseline</t>
-        </is>
-      </c>
-      <c r="JZ3" s="4" t="inlineStr">
-        <is>
-          <t>Effect Estimate</t>
-        </is>
-      </c>
-      <c r="KA3" s="4" t="inlineStr">
-        <is>
-          <t>CI Lower</t>
-        </is>
-      </c>
-      <c r="KB3" s="4" t="inlineStr">
-        <is>
-          <t>CI Upper</t>
-        </is>
-      </c>
-      <c r="KC3" s="4" t="inlineStr">
-        <is>
-          <t>P-value</t>
-        </is>
-      </c>
-      <c r="KD3" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="KE3" s="4" t="inlineStr">
-        <is>
-          <t>Mean</t>
-        </is>
-      </c>
-      <c r="KF3" s="4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="KG3" s="4" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="KH3" s="4" t="inlineStr">
-        <is>
-          <t>Events (n)</t>
-        </is>
-      </c>
-      <c r="KI3" s="4" t="inlineStr">
-        <is>
-          <t>Percentage (%)</t>
-        </is>
-      </c>
-      <c r="KJ3" s="4" t="inlineStr">
-        <is>
-          <t>Change from Baseline</t>
-        </is>
-      </c>
-      <c r="KK3" s="4" t="inlineStr">
-        <is>
-          <t>Effect Estimate</t>
-        </is>
-      </c>
-      <c r="KL3" s="4" t="inlineStr">
-        <is>
-          <t>CI Lower</t>
-        </is>
-      </c>
-      <c r="KM3" s="4" t="inlineStr">
-        <is>
-          <t>CI Upper</t>
-        </is>
-      </c>
-      <c r="KN3" s="4" t="inlineStr">
-        <is>
-          <t>P-value</t>
-        </is>
-      </c>
-      <c r="KO3" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="KP3" s="4" t="inlineStr">
-        <is>
-          <t>Mean</t>
-        </is>
-      </c>
-      <c r="KQ3" s="4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="KR3" s="4" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="KS3" s="4" t="inlineStr">
-        <is>
-          <t>Events (n)</t>
-        </is>
-      </c>
-      <c r="KT3" s="4" t="inlineStr">
-        <is>
-          <t>Percentage (%)</t>
-        </is>
-      </c>
-      <c r="KU3" s="4" t="inlineStr">
-        <is>
-          <t>Change from Baseline</t>
-        </is>
-      </c>
-      <c r="KV3" s="4" t="inlineStr">
-        <is>
-          <t>Effect Estimate</t>
-        </is>
-      </c>
-      <c r="KW3" s="4" t="inlineStr">
-        <is>
-          <t>CI Lower</t>
-        </is>
-      </c>
-      <c r="KX3" s="4" t="inlineStr">
-        <is>
-          <t>CI Upper</t>
-        </is>
-      </c>
-      <c r="KY3" s="4" t="inlineStr">
-        <is>
-          <t>P-value</t>
-        </is>
-      </c>
-      <c r="KZ3" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="LA3" s="4" t="inlineStr">
-        <is>
-          <t>Mean</t>
-        </is>
-      </c>
-      <c r="LB3" s="4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="LC3" s="4" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="LD3" s="4" t="inlineStr">
-        <is>
-          <t>Events (n)</t>
-        </is>
-      </c>
-      <c r="LE3" s="4" t="inlineStr">
-        <is>
-          <t>Percentage (%)</t>
-        </is>
-      </c>
-      <c r="LF3" s="4" t="inlineStr">
-        <is>
-          <t>Change from Baseline</t>
-        </is>
-      </c>
-      <c r="LG3" s="4" t="inlineStr">
-        <is>
-          <t>Effect Estimate</t>
-        </is>
-      </c>
-      <c r="LH3" s="4" t="inlineStr">
-        <is>
-          <t>CI Lower</t>
-        </is>
-      </c>
-      <c r="LI3" s="4" t="inlineStr">
-        <is>
-          <t>CI Upper</t>
-        </is>
-      </c>
-      <c r="LJ3" s="4" t="inlineStr">
-        <is>
-          <t>P-value</t>
-        </is>
-      </c>
-      <c r="LK3" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="LL3" s="4" t="inlineStr">
-        <is>
-          <t>Participants with Event (n)</t>
-        </is>
-      </c>
-      <c r="LM3" s="4" t="inlineStr">
-        <is>
-          <t>Denominator (N)</t>
-        </is>
-      </c>
-      <c r="LN3" s="4" t="inlineStr">
-        <is>
-          <t>Percentage (%)</t>
-        </is>
-      </c>
-      <c r="LO3" s="4" t="inlineStr">
-        <is>
-          <t>Observation Period</t>
-        </is>
-      </c>
-      <c r="LP3" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="LQ3" s="4" t="inlineStr">
-        <is>
-          <t>Participants with Event (n)</t>
-        </is>
-      </c>
-      <c r="LR3" s="4" t="inlineStr">
-        <is>
-          <t>Denominator (N)</t>
-        </is>
-      </c>
-      <c r="LS3" s="4" t="inlineStr">
-        <is>
-          <t>Percentage (%)</t>
-        </is>
-      </c>
-      <c r="LT3" s="4" t="inlineStr">
-        <is>
-          <t>Observation Period</t>
-        </is>
-      </c>
-      <c r="LU3" s="4" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
@@ -5004,87 +4500,57 @@
       <c r="CP4" s="6" t="n"/>
       <c r="CQ4" s="6" t="n"/>
       <c r="CR4" s="6" t="n"/>
-      <c r="CS4" s="7" t="n">
-        <v>29.7</v>
-      </c>
+      <c r="CS4" s="6" t="n"/>
       <c r="CT4" s="6" t="n"/>
       <c r="CU4" s="6" t="n"/>
       <c r="CV4" s="6" t="n"/>
       <c r="CW4" s="6" t="n"/>
       <c r="CX4" s="6" t="n"/>
-      <c r="CY4" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+      <c r="CY4" s="6" t="n"/>
       <c r="CZ4" s="6" t="n"/>
       <c r="DA4" s="6" t="n"/>
       <c r="DB4" s="6" t="n"/>
       <c r="DC4" s="6" t="n"/>
-      <c r="DD4" s="7" t="n">
-        <v>17.2</v>
-      </c>
+      <c r="DD4" s="6" t="n"/>
       <c r="DE4" s="6" t="n"/>
       <c r="DF4" s="6" t="n"/>
       <c r="DG4" s="6" t="n"/>
       <c r="DH4" s="6" t="n"/>
       <c r="DI4" s="6" t="n"/>
-      <c r="DJ4" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+      <c r="DJ4" s="6" t="n"/>
       <c r="DK4" s="6" t="n"/>
       <c r="DL4" s="6" t="n"/>
       <c r="DM4" s="6" t="n"/>
       <c r="DN4" s="6" t="n"/>
-      <c r="DO4" s="7" t="n">
-        <v>28.4</v>
-      </c>
+      <c r="DO4" s="6" t="n"/>
       <c r="DP4" s="6" t="n"/>
       <c r="DQ4" s="6" t="n"/>
       <c r="DR4" s="6" t="n"/>
       <c r="DS4" s="6" t="n"/>
       <c r="DT4" s="6" t="n"/>
-      <c r="DU4" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+      <c r="DU4" s="6" t="n"/>
       <c r="DV4" s="6" t="n"/>
       <c r="DW4" s="6" t="n"/>
       <c r="DX4" s="6" t="n"/>
       <c r="DY4" s="6" t="n"/>
-      <c r="DZ4" s="7" t="n">
-        <v>25</v>
-      </c>
+      <c r="DZ4" s="6" t="n"/>
       <c r="EA4" s="6" t="n"/>
       <c r="EB4" s="6" t="n"/>
       <c r="EC4" s="6" t="n"/>
       <c r="ED4" s="6" t="n"/>
       <c r="EE4" s="6" t="n"/>
-      <c r="EF4" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+      <c r="EF4" s="6" t="n"/>
       <c r="EG4" s="6" t="n"/>
       <c r="EH4" s="6" t="n"/>
       <c r="EI4" s="6" t="n"/>
       <c r="EJ4" s="6" t="n"/>
-      <c r="EK4" s="7" t="n">
-        <v>23.1</v>
-      </c>
+      <c r="EK4" s="6" t="n"/>
       <c r="EL4" s="6" t="n"/>
       <c r="EM4" s="6" t="n"/>
       <c r="EN4" s="6" t="n"/>
       <c r="EO4" s="6" t="n"/>
       <c r="EP4" s="6" t="n"/>
-      <c r="EQ4" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+      <c r="EQ4" s="6" t="n"/>
       <c r="ER4" s="6" t="n"/>
       <c r="ES4" s="6" t="n"/>
       <c r="ET4" s="6" t="n"/>
@@ -5211,66 +4677,6 @@
       <c r="JK4" s="6" t="n"/>
       <c r="JL4" s="6" t="n"/>
       <c r="JM4" s="6" t="n"/>
-      <c r="JN4" s="6" t="n"/>
-      <c r="JO4" s="6" t="n"/>
-      <c r="JP4" s="6" t="n"/>
-      <c r="JQ4" s="6" t="n"/>
-      <c r="JR4" s="6" t="n"/>
-      <c r="JS4" s="6" t="n"/>
-      <c r="JT4" s="6" t="n"/>
-      <c r="JU4" s="6" t="n"/>
-      <c r="JV4" s="6" t="n"/>
-      <c r="JW4" s="6" t="n"/>
-      <c r="JX4" s="6" t="n"/>
-      <c r="JY4" s="6" t="n"/>
-      <c r="JZ4" s="6" t="n"/>
-      <c r="KA4" s="6" t="n"/>
-      <c r="KB4" s="6" t="n"/>
-      <c r="KC4" s="6" t="n"/>
-      <c r="KD4" s="6" t="n"/>
-      <c r="KE4" s="6" t="n"/>
-      <c r="KF4" s="6" t="n"/>
-      <c r="KG4" s="6" t="n"/>
-      <c r="KH4" s="6" t="n"/>
-      <c r="KI4" s="6" t="n"/>
-      <c r="KJ4" s="6" t="n"/>
-      <c r="KK4" s="6" t="n"/>
-      <c r="KL4" s="6" t="n"/>
-      <c r="KM4" s="6" t="n"/>
-      <c r="KN4" s="6" t="n"/>
-      <c r="KO4" s="6" t="n"/>
-      <c r="KP4" s="6" t="n"/>
-      <c r="KQ4" s="6" t="n"/>
-      <c r="KR4" s="6" t="n"/>
-      <c r="KS4" s="6" t="n"/>
-      <c r="KT4" s="6" t="n"/>
-      <c r="KU4" s="6" t="n"/>
-      <c r="KV4" s="6" t="n"/>
-      <c r="KW4" s="6" t="n"/>
-      <c r="KX4" s="6" t="n"/>
-      <c r="KY4" s="6" t="n"/>
-      <c r="KZ4" s="6" t="n"/>
-      <c r="LA4" s="6" t="n"/>
-      <c r="LB4" s="6" t="n"/>
-      <c r="LC4" s="6" t="n"/>
-      <c r="LD4" s="6" t="n"/>
-      <c r="LE4" s="6" t="n"/>
-      <c r="LF4" s="6" t="n"/>
-      <c r="LG4" s="6" t="n"/>
-      <c r="LH4" s="6" t="n"/>
-      <c r="LI4" s="6" t="n"/>
-      <c r="LJ4" s="6" t="n"/>
-      <c r="LK4" s="6" t="n"/>
-      <c r="LL4" s="6" t="n"/>
-      <c r="LM4" s="6" t="n"/>
-      <c r="LN4" s="6" t="n"/>
-      <c r="LO4" s="6" t="n"/>
-      <c r="LP4" s="6" t="n"/>
-      <c r="LQ4" s="6" t="n"/>
-      <c r="LR4" s="6" t="n"/>
-      <c r="LS4" s="6" t="n"/>
-      <c r="LT4" s="6" t="n"/>
-      <c r="LU4" s="6" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
@@ -5487,87 +4893,57 @@
       <c r="CP5" s="9" t="n"/>
       <c r="CQ5" s="9" t="n"/>
       <c r="CR5" s="9" t="n"/>
-      <c r="CS5" s="10" t="n">
-        <v>7.8</v>
-      </c>
+      <c r="CS5" s="9" t="n"/>
       <c r="CT5" s="9" t="n"/>
       <c r="CU5" s="9" t="n"/>
       <c r="CV5" s="9" t="n"/>
       <c r="CW5" s="9" t="n"/>
       <c r="CX5" s="9" t="n"/>
-      <c r="CY5" s="9" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+      <c r="CY5" s="9" t="n"/>
       <c r="CZ5" s="9" t="n"/>
       <c r="DA5" s="9" t="n"/>
       <c r="DB5" s="9" t="n"/>
       <c r="DC5" s="9" t="n"/>
-      <c r="DD5" s="10" t="n">
-        <v>5.9</v>
-      </c>
+      <c r="DD5" s="9" t="n"/>
       <c r="DE5" s="9" t="n"/>
       <c r="DF5" s="9" t="n"/>
       <c r="DG5" s="9" t="n"/>
       <c r="DH5" s="9" t="n"/>
       <c r="DI5" s="9" t="n"/>
-      <c r="DJ5" s="9" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+      <c r="DJ5" s="9" t="n"/>
       <c r="DK5" s="9" t="n"/>
       <c r="DL5" s="9" t="n"/>
       <c r="DM5" s="9" t="n"/>
       <c r="DN5" s="9" t="n"/>
-      <c r="DO5" s="10" t="n">
-        <v>6.5</v>
-      </c>
+      <c r="DO5" s="9" t="n"/>
       <c r="DP5" s="9" t="n"/>
       <c r="DQ5" s="9" t="n"/>
       <c r="DR5" s="9" t="n"/>
       <c r="DS5" s="9" t="n"/>
       <c r="DT5" s="9" t="n"/>
-      <c r="DU5" s="9" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+      <c r="DU5" s="9" t="n"/>
       <c r="DV5" s="9" t="n"/>
       <c r="DW5" s="9" t="n"/>
       <c r="DX5" s="9" t="n"/>
       <c r="DY5" s="9" t="n"/>
-      <c r="DZ5" s="10" t="n">
-        <v>8.199999999999999</v>
-      </c>
+      <c r="DZ5" s="9" t="n"/>
       <c r="EA5" s="9" t="n"/>
       <c r="EB5" s="9" t="n"/>
       <c r="EC5" s="9" t="n"/>
       <c r="ED5" s="9" t="n"/>
       <c r="EE5" s="9" t="n"/>
-      <c r="EF5" s="9" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+      <c r="EF5" s="9" t="n"/>
       <c r="EG5" s="9" t="n"/>
       <c r="EH5" s="9" t="n"/>
       <c r="EI5" s="9" t="n"/>
       <c r="EJ5" s="9" t="n"/>
-      <c r="EK5" s="10" t="n">
-        <v>1.7</v>
-      </c>
+      <c r="EK5" s="9" t="n"/>
       <c r="EL5" s="9" t="n"/>
       <c r="EM5" s="9" t="n"/>
       <c r="EN5" s="9" t="n"/>
       <c r="EO5" s="9" t="n"/>
       <c r="EP5" s="9" t="n"/>
-      <c r="EQ5" s="9" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+      <c r="EQ5" s="9" t="n"/>
       <c r="ER5" s="9" t="n"/>
       <c r="ES5" s="9" t="n"/>
       <c r="ET5" s="9" t="n"/>
@@ -5694,66 +5070,6 @@
       <c r="JK5" s="9" t="n"/>
       <c r="JL5" s="9" t="n"/>
       <c r="JM5" s="9" t="n"/>
-      <c r="JN5" s="9" t="n"/>
-      <c r="JO5" s="9" t="n"/>
-      <c r="JP5" s="9" t="n"/>
-      <c r="JQ5" s="9" t="n"/>
-      <c r="JR5" s="9" t="n"/>
-      <c r="JS5" s="9" t="n"/>
-      <c r="JT5" s="9" t="n"/>
-      <c r="JU5" s="9" t="n"/>
-      <c r="JV5" s="9" t="n"/>
-      <c r="JW5" s="9" t="n"/>
-      <c r="JX5" s="9" t="n"/>
-      <c r="JY5" s="9" t="n"/>
-      <c r="JZ5" s="9" t="n"/>
-      <c r="KA5" s="9" t="n"/>
-      <c r="KB5" s="9" t="n"/>
-      <c r="KC5" s="9" t="n"/>
-      <c r="KD5" s="9" t="n"/>
-      <c r="KE5" s="9" t="n"/>
-      <c r="KF5" s="9" t="n"/>
-      <c r="KG5" s="9" t="n"/>
-      <c r="KH5" s="9" t="n"/>
-      <c r="KI5" s="9" t="n"/>
-      <c r="KJ5" s="9" t="n"/>
-      <c r="KK5" s="9" t="n"/>
-      <c r="KL5" s="9" t="n"/>
-      <c r="KM5" s="9" t="n"/>
-      <c r="KN5" s="9" t="n"/>
-      <c r="KO5" s="9" t="n"/>
-      <c r="KP5" s="9" t="n"/>
-      <c r="KQ5" s="9" t="n"/>
-      <c r="KR5" s="9" t="n"/>
-      <c r="KS5" s="9" t="n"/>
-      <c r="KT5" s="9" t="n"/>
-      <c r="KU5" s="9" t="n"/>
-      <c r="KV5" s="9" t="n"/>
-      <c r="KW5" s="9" t="n"/>
-      <c r="KX5" s="9" t="n"/>
-      <c r="KY5" s="9" t="n"/>
-      <c r="KZ5" s="9" t="n"/>
-      <c r="LA5" s="9" t="n"/>
-      <c r="LB5" s="9" t="n"/>
-      <c r="LC5" s="9" t="n"/>
-      <c r="LD5" s="9" t="n"/>
-      <c r="LE5" s="9" t="n"/>
-      <c r="LF5" s="9" t="n"/>
-      <c r="LG5" s="9" t="n"/>
-      <c r="LH5" s="9" t="n"/>
-      <c r="LI5" s="9" t="n"/>
-      <c r="LJ5" s="9" t="n"/>
-      <c r="LK5" s="9" t="n"/>
-      <c r="LL5" s="9" t="n"/>
-      <c r="LM5" s="9" t="n"/>
-      <c r="LN5" s="9" t="n"/>
-      <c r="LO5" s="9" t="n"/>
-      <c r="LP5" s="9" t="n"/>
-      <c r="LQ5" s="9" t="n"/>
-      <c r="LR5" s="9" t="n"/>
-      <c r="LS5" s="9" t="n"/>
-      <c r="LT5" s="9" t="n"/>
-      <c r="LU5" s="9" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -5955,17 +5271,29 @@
       <c r="CW6" s="6" t="n"/>
       <c r="CX6" s="6" t="n"/>
       <c r="CY6" s="6" t="n"/>
-      <c r="CZ6" s="6" t="n"/>
+      <c r="CZ6" s="7" t="n">
+        <v>-0.95</v>
+      </c>
       <c r="DA6" s="6" t="n"/>
       <c r="DB6" s="6" t="n"/>
       <c r="DC6" s="6" t="n"/>
       <c r="DD6" s="6" t="n"/>
-      <c r="DE6" s="6" t="n"/>
+      <c r="DE6" s="7" t="n">
+        <v>-0.95</v>
+      </c>
       <c r="DF6" s="6" t="n"/>
       <c r="DG6" s="6" t="n"/>
       <c r="DH6" s="6" t="n"/>
-      <c r="DI6" s="6" t="n"/>
-      <c r="DJ6" s="6" t="n"/>
+      <c r="DI6" s="6" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="DJ6" s="6" t="inlineStr">
+        <is>
+          <t>kg/m2</t>
+        </is>
+      </c>
       <c r="DK6" s="6" t="n"/>
       <c r="DL6" s="6" t="n"/>
       <c r="DM6" s="6" t="n"/>
@@ -6010,29 +5338,17 @@
       <c r="EZ6" s="6" t="n"/>
       <c r="FA6" s="6" t="n"/>
       <c r="FB6" s="6" t="n"/>
-      <c r="FC6" s="7" t="n">
-        <v>-0.95</v>
-      </c>
+      <c r="FC6" s="6" t="n"/>
       <c r="FD6" s="6" t="n"/>
       <c r="FE6" s="6" t="n"/>
       <c r="FF6" s="6" t="n"/>
       <c r="FG6" s="6" t="n"/>
-      <c r="FH6" s="7" t="n">
-        <v>-0.95</v>
-      </c>
+      <c r="FH6" s="6" t="n"/>
       <c r="FI6" s="6" t="n"/>
       <c r="FJ6" s="6" t="n"/>
       <c r="FK6" s="6" t="n"/>
-      <c r="FL6" s="6" t="inlineStr">
-        <is>
-          <t>0.001</t>
-        </is>
-      </c>
-      <c r="FM6" s="6" t="inlineStr">
-        <is>
-          <t>kg/m2</t>
-        </is>
-      </c>
+      <c r="FL6" s="6" t="n"/>
+      <c r="FM6" s="6" t="n"/>
       <c r="FN6" s="6" t="n"/>
       <c r="FO6" s="6" t="n"/>
       <c r="FP6" s="6" t="n"/>
@@ -6132,85 +5448,25 @@
       <c r="JF6" s="6" t="n"/>
       <c r="JG6" s="6" t="n"/>
       <c r="JH6" s="6" t="n"/>
-      <c r="JI6" s="6" t="n"/>
-      <c r="JJ6" s="6" t="n"/>
-      <c r="JK6" s="6" t="n"/>
-      <c r="JL6" s="6" t="n"/>
-      <c r="JM6" s="6" t="n"/>
-      <c r="JN6" s="6" t="n"/>
-      <c r="JO6" s="6" t="n"/>
-      <c r="JP6" s="6" t="n"/>
-      <c r="JQ6" s="6" t="n"/>
-      <c r="JR6" s="6" t="n"/>
-      <c r="JS6" s="6" t="n"/>
-      <c r="JT6" s="6" t="n"/>
-      <c r="JU6" s="6" t="n"/>
-      <c r="JV6" s="6" t="n"/>
-      <c r="JW6" s="6" t="n"/>
-      <c r="JX6" s="6" t="n"/>
-      <c r="JY6" s="6" t="n"/>
-      <c r="JZ6" s="6" t="n"/>
-      <c r="KA6" s="6" t="n"/>
-      <c r="KB6" s="6" t="n"/>
-      <c r="KC6" s="6" t="n"/>
-      <c r="KD6" s="6" t="n"/>
-      <c r="KE6" s="6" t="n"/>
-      <c r="KF6" s="6" t="n"/>
-      <c r="KG6" s="6" t="n"/>
-      <c r="KH6" s="6" t="n"/>
-      <c r="KI6" s="6" t="n"/>
-      <c r="KJ6" s="6" t="n"/>
-      <c r="KK6" s="6" t="n"/>
-      <c r="KL6" s="6" t="n"/>
-      <c r="KM6" s="6" t="n"/>
-      <c r="KN6" s="6" t="n"/>
-      <c r="KO6" s="6" t="n"/>
-      <c r="KP6" s="6" t="n"/>
-      <c r="KQ6" s="6" t="n"/>
-      <c r="KR6" s="6" t="n"/>
-      <c r="KS6" s="6" t="n"/>
-      <c r="KT6" s="6" t="n"/>
-      <c r="KU6" s="6" t="n"/>
-      <c r="KV6" s="6" t="n"/>
-      <c r="KW6" s="6" t="n"/>
-      <c r="KX6" s="6" t="n"/>
-      <c r="KY6" s="6" t="n"/>
-      <c r="KZ6" s="6" t="n"/>
-      <c r="LA6" s="6" t="n"/>
-      <c r="LB6" s="6" t="n"/>
-      <c r="LC6" s="6" t="n"/>
-      <c r="LD6" s="6" t="n"/>
-      <c r="LE6" s="6" t="n"/>
-      <c r="LF6" s="6" t="n"/>
-      <c r="LG6" s="6" t="n"/>
-      <c r="LH6" s="6" t="n"/>
-      <c r="LI6" s="6" t="n"/>
-      <c r="LJ6" s="6" t="n"/>
-      <c r="LK6" s="6" t="n"/>
-      <c r="LL6" s="6" t="n">
+      <c r="JI6" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="LM6" s="6" t="n">
+      <c r="JJ6" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="LN6" s="7" t="n">
+      <c r="JK6" s="7" t="n">
         <v>8.1</v>
       </c>
-      <c r="LO6" s="6" t="inlineStr">
+      <c r="JL6" s="6" t="inlineStr">
         <is>
           <t>Safety observation period</t>
         </is>
       </c>
-      <c r="LP6" s="6" t="inlineStr">
+      <c r="JM6" s="6" t="inlineStr">
         <is>
           <t>events</t>
         </is>
       </c>
-      <c r="LQ6" s="6" t="n"/>
-      <c r="LR6" s="6" t="n"/>
-      <c r="LS6" s="6" t="n"/>
-      <c r="LT6" s="6" t="n"/>
-      <c r="LU6" s="6" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
@@ -6412,17 +5668,29 @@
       <c r="CW7" s="9" t="n"/>
       <c r="CX7" s="9" t="n"/>
       <c r="CY7" s="9" t="n"/>
-      <c r="CZ7" s="9" t="n"/>
+      <c r="CZ7" s="10" t="n">
+        <v>-0.25</v>
+      </c>
       <c r="DA7" s="9" t="n"/>
       <c r="DB7" s="9" t="n"/>
       <c r="DC7" s="9" t="n"/>
       <c r="DD7" s="9" t="n"/>
-      <c r="DE7" s="9" t="n"/>
+      <c r="DE7" s="10" t="n">
+        <v>-0.25</v>
+      </c>
       <c r="DF7" s="9" t="n"/>
       <c r="DG7" s="9" t="n"/>
       <c r="DH7" s="9" t="n"/>
-      <c r="DI7" s="9" t="n"/>
-      <c r="DJ7" s="9" t="n"/>
+      <c r="DI7" s="9" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="DJ7" s="9" t="inlineStr">
+        <is>
+          <t>kg/m2</t>
+        </is>
+      </c>
       <c r="DK7" s="9" t="n"/>
       <c r="DL7" s="9" t="n"/>
       <c r="DM7" s="9" t="n"/>
@@ -6467,29 +5735,17 @@
       <c r="EZ7" s="9" t="n"/>
       <c r="FA7" s="9" t="n"/>
       <c r="FB7" s="9" t="n"/>
-      <c r="FC7" s="10" t="n">
-        <v>-0.25</v>
-      </c>
+      <c r="FC7" s="9" t="n"/>
       <c r="FD7" s="9" t="n"/>
       <c r="FE7" s="9" t="n"/>
       <c r="FF7" s="9" t="n"/>
       <c r="FG7" s="9" t="n"/>
-      <c r="FH7" s="10" t="n">
-        <v>-0.25</v>
-      </c>
+      <c r="FH7" s="9" t="n"/>
       <c r="FI7" s="9" t="n"/>
       <c r="FJ7" s="9" t="n"/>
       <c r="FK7" s="9" t="n"/>
-      <c r="FL7" s="9" t="inlineStr">
-        <is>
-          <t>0.001</t>
-        </is>
-      </c>
-      <c r="FM7" s="9" t="inlineStr">
-        <is>
-          <t>kg/m2</t>
-        </is>
-      </c>
+      <c r="FL7" s="9" t="n"/>
+      <c r="FM7" s="9" t="n"/>
       <c r="FN7" s="9" t="n"/>
       <c r="FO7" s="9" t="n"/>
       <c r="FP7" s="9" t="n"/>
@@ -6589,123 +5845,58 @@
       <c r="JF7" s="9" t="n"/>
       <c r="JG7" s="9" t="n"/>
       <c r="JH7" s="9" t="n"/>
-      <c r="JI7" s="9" t="n"/>
-      <c r="JJ7" s="9" t="n"/>
-      <c r="JK7" s="9" t="n"/>
-      <c r="JL7" s="9" t="n"/>
-      <c r="JM7" s="9" t="n"/>
-      <c r="JN7" s="9" t="n"/>
-      <c r="JO7" s="9" t="n"/>
-      <c r="JP7" s="9" t="n"/>
-      <c r="JQ7" s="9" t="n"/>
-      <c r="JR7" s="9" t="n"/>
-      <c r="JS7" s="9" t="n"/>
-      <c r="JT7" s="9" t="n"/>
-      <c r="JU7" s="9" t="n"/>
-      <c r="JV7" s="9" t="n"/>
-      <c r="JW7" s="9" t="n"/>
-      <c r="JX7" s="9" t="n"/>
-      <c r="JY7" s="9" t="n"/>
-      <c r="JZ7" s="9" t="n"/>
-      <c r="KA7" s="9" t="n"/>
-      <c r="KB7" s="9" t="n"/>
-      <c r="KC7" s="9" t="n"/>
-      <c r="KD7" s="9" t="n"/>
-      <c r="KE7" s="9" t="n"/>
-      <c r="KF7" s="9" t="n"/>
-      <c r="KG7" s="9" t="n"/>
-      <c r="KH7" s="9" t="n"/>
-      <c r="KI7" s="9" t="n"/>
-      <c r="KJ7" s="9" t="n"/>
-      <c r="KK7" s="9" t="n"/>
-      <c r="KL7" s="9" t="n"/>
-      <c r="KM7" s="9" t="n"/>
-      <c r="KN7" s="9" t="n"/>
-      <c r="KO7" s="9" t="n"/>
-      <c r="KP7" s="9" t="n"/>
-      <c r="KQ7" s="9" t="n"/>
-      <c r="KR7" s="9" t="n"/>
-      <c r="KS7" s="9" t="n"/>
-      <c r="KT7" s="9" t="n"/>
-      <c r="KU7" s="9" t="n"/>
-      <c r="KV7" s="9" t="n"/>
-      <c r="KW7" s="9" t="n"/>
-      <c r="KX7" s="9" t="n"/>
-      <c r="KY7" s="9" t="n"/>
-      <c r="KZ7" s="9" t="n"/>
-      <c r="LA7" s="9" t="n"/>
-      <c r="LB7" s="9" t="n"/>
-      <c r="LC7" s="9" t="n"/>
-      <c r="LD7" s="9" t="n"/>
-      <c r="LE7" s="9" t="n"/>
-      <c r="LF7" s="9" t="n"/>
-      <c r="LG7" s="9" t="n"/>
-      <c r="LH7" s="9" t="n"/>
-      <c r="LI7" s="9" t="n"/>
-      <c r="LJ7" s="9" t="n"/>
-      <c r="LK7" s="9" t="n"/>
-      <c r="LL7" s="9" t="n"/>
-      <c r="LM7" s="9" t="n"/>
-      <c r="LN7" s="9" t="n"/>
-      <c r="LO7" s="9" t="n"/>
-      <c r="LP7" s="9" t="n"/>
-      <c r="LQ7" s="9" t="n">
+      <c r="JI7" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="LR7" s="9" t="n">
+      <c r="JJ7" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="LS7" s="10" t="n">
+      <c r="JK7" s="10" t="n">
         <v>25.7</v>
       </c>
-      <c r="LT7" s="9" t="inlineStr">
+      <c r="JL7" s="9" t="inlineStr">
         <is>
           <t>Safety observation period</t>
         </is>
       </c>
-      <c r="LU7" s="9" t="inlineStr">
+      <c r="JM7" s="9" t="inlineStr">
         <is>
           <t>events</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="48">
+  <mergeCells count="42">
+    <mergeCell ref="JI2:JM2"/>
     <mergeCell ref="Y2:AA2"/>
     <mergeCell ref="AE2:AG2"/>
     <mergeCell ref="P2:R2"/>
-    <mergeCell ref="JI2:JS2"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="GU2:HE2"/>
     <mergeCell ref="AW2:BG2"/>
-    <mergeCell ref="KE2:KO2"/>
     <mergeCell ref="FY2:GI2"/>
-    <mergeCell ref="AW1:LK1"/>
+    <mergeCell ref="AW1:JH1"/>
     <mergeCell ref="DV2:EF2"/>
     <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="ER2:FB2"/>
-    <mergeCell ref="JT2:KD2"/>
     <mergeCell ref="GJ2:GT2"/>
+    <mergeCell ref="JI1:JM1"/>
     <mergeCell ref="BH2:BR2"/>
     <mergeCell ref="CZ2:DJ2"/>
-    <mergeCell ref="LQ2:LU2"/>
     <mergeCell ref="AH2:AJ2"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="AQ2:AR2"/>
     <mergeCell ref="AL1:AN1"/>
     <mergeCell ref="FN2:FX2"/>
     <mergeCell ref="AS2:AT2"/>
-    <mergeCell ref="KP2:KZ2"/>
     <mergeCell ref="IX2:JH2"/>
     <mergeCell ref="CD2:CN2"/>
-    <mergeCell ref="LL2:LP2"/>
     <mergeCell ref="M1:AK1"/>
     <mergeCell ref="IB2:IL2"/>
     <mergeCell ref="AO1:AV1"/>
     <mergeCell ref="HF2:HP2"/>
     <mergeCell ref="V2:X2"/>
-    <mergeCell ref="LL1:LU1"/>
     <mergeCell ref="EG2:EQ2"/>
     <mergeCell ref="DK2:DU2"/>
     <mergeCell ref="FC2:FM2"/>
@@ -6715,7 +5906,6 @@
     <mergeCell ref="AU2:AV2"/>
     <mergeCell ref="HQ2:IA2"/>
     <mergeCell ref="BS2:CC2"/>
-    <mergeCell ref="LA2:LK2"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="S2:U2"/>
     <mergeCell ref="CO2:CY2"/>
@@ -13363,13 +12553,9 @@
         <v>1.887</v>
       </c>
       <c r="J5" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="19" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
+        <v>1e-05</v>
+      </c>
+      <c r="K5" s="19" t="n"/>
       <c r="L5" s="18" t="inlineStr">
         <is>
           <t>p_between=0.0000</t>
@@ -13415,11 +12601,7 @@
       <c r="J6" s="19" t="n">
         <v>0.0034</v>
       </c>
-      <c r="K6" s="19" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
+      <c r="K6" s="19" t="n"/>
       <c r="L6" s="18" t="inlineStr">
         <is>
           <t>p_between=0.0000</t>
@@ -13465,11 +12647,7 @@
       <c r="J7" s="19" t="n">
         <v>0.0034</v>
       </c>
-      <c r="K7" s="19" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
+      <c r="K7" s="19" t="n"/>
       <c r="L7" s="18" t="inlineStr">
         <is>
           <t>p_between=0.0000</t>
@@ -13513,13 +12691,9 @@
         <v>1.887</v>
       </c>
       <c r="J8" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="19" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
+        <v>1e-05</v>
+      </c>
+      <c r="K8" s="19" t="n"/>
       <c r="L8" s="18" t="inlineStr">
         <is>
           <t>p_between=0.0000</t>
@@ -14515,7 +13689,7 @@
     <row r="3">
       <c r="A3" s="25" t="inlineStr">
         <is>
-          <t>Adaptation Strategy: Trials evaluate 2 distinct active ingredients (Metformin, Orlistat) with differing measurement endpoints and follow-up horizons. MANDOROS automatically adapted by: (1) Running direct pooling on exact parameter matches where available; (2) Constructing Clinical Outcome Domains and applying scale-free Standardized Mean Differences (Hedges' g) to bridge differing metrics (e.g. BMI vs. Body Weight vs. Waist Circumference); (3) Performing Bucher anchored indirect comparisons against common control arms with SUCRA ranking; and (4) Normalizing durations into monthly rate-of-change trajectories in predictive meta-regression. Specifically, because DPP_Extended_Cohort measured 'primary outcome' over nan nan (Reported in protocol) and DPP_Metformin_2012 measured 'weight loss &gt;= 5%' over 2.0 years (Metformin 850mg (850.0 mg - experimental); Placebo (nan nan - placebo)), MANDOROS automatically applied Tier 2 Scale-Free Standardized Mean Difference (Hedges' g SMD) and clinical domain bridging (Other Clinical &amp; Laboratory Endpoints) to synthesize their therapeutic impact on a unified, dimensionless scale while computing monthly rate-of-change trajectories to reconcile differing follow-up horizons.</t>
+          <t>Adaptation Strategy: Trials evaluate 2 distinct active ingredients (Metformin, Orlistat) with differing measurement endpoints and follow-up horizons. MANDOROS automatically adapted by: (1) Running direct pooling on exact parameter matches where available; (2) Constructing Clinical Outcome Domains and applying scale-free Standardized Mean Differences (Hedges' g) to bridge differing metrics (e.g. BMI vs. Body Weight vs. Waist Circumference); (3) Performing Bucher anchored indirect comparisons against common control arms with SUCRA ranking; and (4) Normalizing durations into monthly rate-of-change trajectories in predictive meta-regression. Specifically, because DPP_Extended_Cohort measured 'primary outcome' over nan nan (Reported in protocol) and DPP_Metformin_2012 measured 'high adherence' over 2.0 years (Metformin 850mg (850.0 mg - experimental); Placebo (nan nan - placebo)), MANDOROS automatically applied Tier 2 Scale-Free Standardized Mean Difference (Hedges' g SMD) and clinical domain bridging (Other Clinical &amp; Laboratory Endpoints) to synthesize their therapeutic impact on a unified, dimensionless scale while computing monthly rate-of-change trajectories to reconcile differing follow-up horizons.</t>
         </is>
       </c>
     </row>
@@ -15061,7 +14235,7 @@
       </c>
       <c r="M6" s="18" t="inlineStr">
         <is>
-          <t>NOT_ESTIMABLE: Domain 'Anthropometric &amp; Weight Management' contains 3 distinct clinical constructs (waist_circumference, weight_loss, bmi). Omnibus pooling of clinically unrelated endpoints into a single SMD is methodologically invalid.</t>
+          <t>NOT_ESTIMABLE: Domain 'Anthropometric &amp; Weight Management' contains 3 distinct clinical constructs (weight_loss, waist_circumference, bmi). Omnibus pooling of clinically unrelated endpoints into a single SMD is methodologically invalid.</t>
         </is>
       </c>
     </row>
@@ -15401,13 +14575,9 @@
         <v>1.887</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="19" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
+        <v>1e-05</v>
+      </c>
+      <c r="I19" s="19" t="n"/>
       <c r="J19" s="19" t="n">
         <v>56.192</v>
       </c>
@@ -15452,11 +14622,7 @@
       <c r="H20" s="19" t="n">
         <v>0.0034</v>
       </c>
-      <c r="I20" s="19" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
+      <c r="I20" s="19" t="n"/>
       <c r="J20" s="19" t="n">
         <v>56.192</v>
       </c>
@@ -15501,11 +14667,7 @@
       <c r="H21" s="19" t="n">
         <v>0.0034</v>
       </c>
-      <c r="I21" s="19" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
+      <c r="I21" s="19" t="n"/>
       <c r="J21" s="19" t="n">
         <v>56.192</v>
       </c>
@@ -15548,13 +14710,9 @@
         <v>1.887</v>
       </c>
       <c r="H22" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="19" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
+        <v>1e-05</v>
+      </c>
+      <c r="I22" s="19" t="n"/>
       <c r="J22" s="19" t="n">
         <v>56.192</v>
       </c>
@@ -29607,11 +28765,9 @@
         <v>2155</v>
       </c>
       <c r="H2" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="34" t="n">
-        <v>0</v>
-      </c>
+        <v>1e-05</v>
+      </c>
+      <c r="I2" s="30" t="n"/>
       <c r="J2" s="33" t="n">
         <v>56.192</v>
       </c>
@@ -29656,9 +28812,7 @@
       <c r="H3" s="35" t="n">
         <v>0.003401282133642658</v>
       </c>
-      <c r="I3" s="34" t="n">
-        <v>0</v>
-      </c>
+      <c r="I3" s="30" t="n"/>
       <c r="J3" s="33" t="n">
         <v>56.192</v>
       </c>
@@ -29703,9 +28857,7 @@
       <c r="H4" s="35" t="n">
         <v>0.003401282133642658</v>
       </c>
-      <c r="I4" s="34" t="n">
-        <v>0</v>
-      </c>
+      <c r="I4" s="30" t="n"/>
       <c r="J4" s="33" t="n">
         <v>56.192</v>
       </c>
@@ -29748,11 +28900,9 @@
         <v>2155</v>
       </c>
       <c r="H5" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="34" t="n">
-        <v>0</v>
-      </c>
+        <v>1e-05</v>
+      </c>
+      <c r="I5" s="30" t="n"/>
       <c r="J5" s="33" t="n">
         <v>56.192</v>
       </c>
@@ -29962,7 +29112,7 @@
         <v>0.02637985556246275</v>
       </c>
       <c r="E2" s="35" t="n">
-        <v>0</v>
+        <v>1e-05</v>
       </c>
       <c r="F2" s="32" t="n">
         <v>3</v>
@@ -57407,7 +56557,7 @@
         </is>
       </c>
       <c r="J6" s="19" t="n">
-        <v>0</v>
+        <v>1e-05</v>
       </c>
       <c r="K6" s="19" t="inlineStr">
         <is>
@@ -57629,7 +56779,7 @@
         </is>
       </c>
       <c r="I6" s="19" t="n">
-        <v>0</v>
+        <v>1e-05</v>
       </c>
       <c r="J6" s="19" t="inlineStr">
         <is>

--- a/outputs/analysis/Mixed_Metabolic_Cohort/Mixed_Metabolic_Cohort_MANDOROS_Master_Report.xlsx
+++ b/outputs/analysis/Mixed_Metabolic_Cohort/Mixed_Metabolic_Cohort_MANDOROS_Master_Report.xlsx
@@ -13689,7 +13689,7 @@
     <row r="3">
       <c r="A3" s="25" t="inlineStr">
         <is>
-          <t>Adaptation Strategy: Trials evaluate 2 distinct active ingredients (Metformin, Orlistat) with differing measurement endpoints and follow-up horizons. MANDOROS automatically adapted by: (1) Running direct pooling on exact parameter matches where available; (2) Constructing Clinical Outcome Domains and applying scale-free Standardized Mean Differences (Hedges' g) to bridge differing metrics (e.g. BMI vs. Body Weight vs. Waist Circumference); (3) Performing Bucher anchored indirect comparisons against common control arms with SUCRA ranking; and (4) Normalizing durations into monthly rate-of-change trajectories in predictive meta-regression. Specifically, because DPP_Extended_Cohort measured 'primary outcome' over nan nan (Reported in protocol) and DPP_Metformin_2012 measured 'high adherence' over 2.0 years (Metformin 850mg (850.0 mg - experimental); Placebo (nan nan - placebo)), MANDOROS automatically applied Tier 2 Scale-Free Standardized Mean Difference (Hedges' g SMD) and clinical domain bridging (Other Clinical &amp; Laboratory Endpoints) to synthesize their therapeutic impact on a unified, dimensionless scale while computing monthly rate-of-change trajectories to reconcile differing follow-up horizons.</t>
+          <t>Adaptation Strategy: Trials evaluate 2 distinct active ingredients (Metformin, Orlistat) with differing measurement endpoints and follow-up horizons. MANDOROS automatically adapted by: (1) Running direct pooling on exact parameter matches where available; (2) Constructing Clinical Outcome Domains and applying scale-free Standardized Mean Differences (Hedges' g) to bridge differing metrics (e.g. BMI vs. Body Weight vs. Waist Circumference); (3) Performing Bucher anchored indirect comparisons against common control arms with SUCRA ranking; and (4) Normalizing durations into monthly rate-of-change trajectories in predictive meta-regression. Specifically, because DPP_Extended_Cohort measured 'primary outcome' over nan nan (Reported in protocol) and DPP_Metformin_2012 measured 'weight loss &gt;= 5%' over 2.0 years (Metformin 850mg (850.0 mg - experimental); Placebo (nan nan - placebo)), MANDOROS automatically applied Tier 2 Scale-Free Standardized Mean Difference (Hedges' g SMD) and clinical domain bridging (Other Clinical &amp; Laboratory Endpoints) to synthesize their therapeutic impact on a unified, dimensionless scale while computing monthly rate-of-change trajectories to reconcile differing follow-up horizons.</t>
         </is>
       </c>
     </row>
@@ -14235,7 +14235,7 @@
       </c>
       <c r="M6" s="18" t="inlineStr">
         <is>
-          <t>NOT_ESTIMABLE: Domain 'Anthropometric &amp; Weight Management' contains 3 distinct clinical constructs (weight_loss, waist_circumference, bmi). Omnibus pooling of clinically unrelated endpoints into a single SMD is methodologically invalid.</t>
+          <t>NOT_ESTIMABLE: Domain 'Anthropometric &amp; Weight Management' contains 3 distinct clinical constructs (waist_circumference, bmi, weight_loss). Omnibus pooling of clinically unrelated endpoints into a single SMD is methodologically invalid.</t>
         </is>
       </c>
     </row>

--- a/outputs/analysis/Mixed_Metabolic_Cohort/Mixed_Metabolic_Cohort_MANDOROS_Master_Report.xlsx
+++ b/outputs/analysis/Mixed_Metabolic_Cohort/Mixed_Metabolic_Cohort_MANDOROS_Master_Report.xlsx
@@ -13689,7 +13689,7 @@
     <row r="3">
       <c r="A3" s="25" t="inlineStr">
         <is>
-          <t>Adaptation Strategy: Trials evaluate 2 distinct active ingredients (Metformin, Orlistat) with differing measurement endpoints and follow-up horizons. MANDOROS automatically adapted by: (1) Running direct pooling on exact parameter matches where available; (2) Constructing Clinical Outcome Domains and applying scale-free Standardized Mean Differences (Hedges' g) to bridge differing metrics (e.g. BMI vs. Body Weight vs. Waist Circumference); (3) Performing Bucher anchored indirect comparisons against common control arms with SUCRA ranking; and (4) Normalizing durations into monthly rate-of-change trajectories in predictive meta-regression. Specifically, because DPP_Extended_Cohort measured 'primary outcome' over nan nan (Reported in protocol) and DPP_Metformin_2012 measured 'weight loss &gt;= 5%' over 2.0 years (Metformin 850mg (850.0 mg - experimental); Placebo (nan nan - placebo)), MANDOROS automatically applied Tier 2 Scale-Free Standardized Mean Difference (Hedges' g SMD) and clinical domain bridging (Other Clinical &amp; Laboratory Endpoints) to synthesize their therapeutic impact on a unified, dimensionless scale while computing monthly rate-of-change trajectories to reconcile differing follow-up horizons.</t>
+          <t>Adaptation Strategy: Trials evaluate 2 distinct active ingredients (Metformin, Orlistat) with differing measurement endpoints and follow-up horizons. MANDOROS automatically adapted by: (1) Running direct pooling on exact parameter matches where available; (2) Constructing Clinical Outcome Domains and applying scale-free Standardized Mean Differences (Hedges' g) to bridge differing metrics (e.g. BMI vs. Body Weight vs. Waist Circumference); (3) Performing Bucher anchored indirect comparisons against common control arms with SUCRA ranking; and (4) Normalizing durations into monthly rate-of-change trajectories in predictive meta-regression. Specifically, because DPP_Extended_Cohort measured 'primary outcome' over nan nan (Reported in protocol) and DPP_Metformin_2012 measured 'weight_loss' over 2.0 years (Metformin 850mg (850.0 mg - experimental); Placebo (nan nan - placebo)), MANDOROS automatically applied Tier 2 Scale-Free Standardized Mean Difference (Hedges' g SMD) and clinical domain bridging (Other Clinical &amp; Laboratory Endpoints) to synthesize their therapeutic impact on a unified, dimensionless scale while computing monthly rate-of-change trajectories to reconcile differing follow-up horizons.</t>
         </is>
       </c>
     </row>
@@ -14235,7 +14235,7 @@
       </c>
       <c r="M6" s="18" t="inlineStr">
         <is>
-          <t>NOT_ESTIMABLE: Domain 'Anthropometric &amp; Weight Management' contains 3 distinct clinical constructs (waist_circumference, bmi, weight_loss). Omnibus pooling of clinically unrelated endpoints into a single SMD is methodologically invalid.</t>
+          <t>NOT_ESTIMABLE: Domain 'Anthropometric &amp; Weight Management' contains 3 distinct clinical constructs (waist_circumference, weight_loss, bmi). Omnibus pooling of clinically unrelated endpoints into a single SMD is methodologically invalid.</t>
         </is>
       </c>
     </row>
